--- a/events/Pitesti_2021_MAR/Pitesti_2021_MAR_Results.xlsx
+++ b/events/Pitesti_2021_MAR/Pitesti_2021_MAR_Results.xlsx
@@ -33230,7 +33230,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eavan O’KEEFFE</t>
+          <t>Eavan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>O’KEEFFE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/events/Pitesti_2021_MAR/Pitesti_2021_MAR_Results.xlsx
+++ b/events/Pitesti_2021_MAR/Pitesti_2021_MAR_Results.xlsx
@@ -604,6 +604,11 @@
           <t>01:32:30.920</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>104760</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1470,6 +1475,11 @@
           <t>01:39:48.750</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>110845</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1996,6 +2006,11 @@
           <t>01:46:26.840</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>112334</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2253,6 +2268,11 @@
           <t>01:06:05.790</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>106866</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2773,6 +2793,11 @@
       <c r="L35" t="n">
         <v>34</v>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>97015</t>
+        </is>
+      </c>
       <c r="X35" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -4307,6 +4332,11 @@
           <t>00:17:29.740</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4952,6 +4982,11 @@
           <t>00:14:52.400</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5337,6 +5372,11 @@
           <t>00:15:24.490</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>111198</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5787,6 +5827,11 @@
           <t>00:16:53.260</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>65545</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5847,6 +5892,11 @@
           <t>00:17:25.110</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5907,6 +5957,11 @@
           <t>00:18:03.510</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>117389</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7533,6 +7588,11 @@
           <t>01:37:12.380</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>112336</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7796,6 +7856,11 @@
           <t>01:41:18.200</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>112337</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8656,6 +8721,11 @@
           <t>00:19:11.790</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8852,6 +8922,11 @@
           <t>00:19:48.920</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>106866</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9182,6 +9257,11 @@
           <t>00:20:46.360</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>117391</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9914,6 +9994,11 @@
           <t>00:17:06.860</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11775,6 +11860,11 @@
           <t>00:17:28.610</t>
         </is>
       </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12440,6 +12530,11 @@
           <t>00:14:36.500</t>
         </is>
       </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13517,6 +13612,11 @@
           <t>98601</t>
         </is>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>104760</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13939,6 +14039,11 @@
           <t>01:30:52.570</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>110845</t>
+        </is>
+      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>110846</t>
@@ -14150,6 +14255,11 @@
           <t>01:32:20.930</t>
         </is>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>111770</t>
+        </is>
+      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>111773</t>
@@ -16184,6 +16294,11 @@
           <t>01:51:32.120</t>
         </is>
       </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17115,6 +17230,16 @@
           <t>01:29:20.260</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>112336</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>112337</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -17398,6 +17523,11 @@
           <t>112351</t>
         </is>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>112350</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -19742,6 +19872,11 @@
           <t>01:41:00.590</t>
         </is>
       </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>116917</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -19804,6 +19939,11 @@
           <t>01:41:04.300</t>
         </is>
       </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>109339</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -20670,6 +20810,11 @@
           <t>01:45:03.670</t>
         </is>
       </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>110840</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -21469,6 +21614,11 @@
           <t>01:55:45.680</t>
         </is>
       </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>116930</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -21927,6 +22077,11 @@
           <t>01:22:40.470</t>
         </is>
       </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -22257,6 +22412,11 @@
           <t>01:26:43.570</t>
         </is>
       </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>106866</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -22587,6 +22747,11 @@
           <t>01:30:11.500</t>
         </is>
       </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>117391</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -23118,6 +23283,11 @@
           <t>02:06:30.830</t>
         </is>
       </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -24285,6 +24455,11 @@
           <t>02:08:18.750</t>
         </is>
       </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -24481,6 +24656,11 @@
           <t>02:09:18.370</t>
         </is>
       </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -24610,6 +24790,11 @@
           <t>02:10:30.630</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -25610,6 +25795,11 @@
           <t>02:07:20.660</t>
         </is>
       </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -26610,6 +26800,11 @@
           <t>02:15:10.330</t>
         </is>
       </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -27007,6 +27202,11 @@
           <t>02:23:22.770</t>
         </is>
       </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>65545</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -27203,6 +27403,11 @@
           <t>02:17:07.760</t>
         </is>
       </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>117389</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -27265,6 +27470,11 @@
           <t>02:22:00.620</t>
         </is>
       </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -27837,6 +28047,11 @@
           <t>01:35:19.280</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>116917</t>
+        </is>
+      </c>
       <c r="S414" t="inlineStr">
         <is>
           <t>116919</t>
@@ -28557,6 +28772,11 @@
           <t>112737</t>
         </is>
       </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>112783</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -28979,6 +29199,11 @@
           <t>01:45:58.030</t>
         </is>
       </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>116930</t>
+        </is>
+      </c>
       <c r="S430" t="inlineStr">
         <is>
           <t>116931</t>
@@ -29123,6 +29348,11 @@
           <t>118118</t>
         </is>
       </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>118119</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -29676,6 +29906,11 @@
           <t>48163</t>
         </is>
       </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -29882,6 +30117,11 @@
           <t>02:01:33.270</t>
         </is>
       </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
       <c r="S443" t="inlineStr">
         <is>
           <t>65440</t>
@@ -30730,6 +30970,11 @@
           <t>02:00:14.430</t>
         </is>
       </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
       <c r="S455" t="inlineStr">
         <is>
           <t>98391</t>
@@ -31578,6 +31823,11 @@
           <t>01:59:04.300</t>
         </is>
       </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S467" t="inlineStr">
         <is>
           <t>88713</t>
@@ -31794,6 +32044,11 @@
           <t>87418</t>
         </is>
       </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -32576,6 +32831,11 @@
           <t>02:07:17.850</t>
         </is>
       </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>116921</t>
+        </is>
+      </c>
       <c r="S481" t="inlineStr">
         <is>
           <t>47482</t>
@@ -32648,6 +32908,11 @@
           <t>38994</t>
         </is>
       </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>49779</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -32710,6 +32975,11 @@
           <t>02:08:56.500</t>
         </is>
       </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>85380</t>
+        </is>
+      </c>
       <c r="S483" t="inlineStr">
         <is>
           <t>87666</t>
@@ -32782,6 +33052,11 @@
           <t>95552</t>
         </is>
       </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>111198</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -33108,6 +33383,11 @@
       </c>
       <c r="L489" t="n">
         <v>620</v>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>98131</t>
+        </is>
       </c>
       <c r="S489" t="inlineStr">
         <is>
@@ -33197,7 +33477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D336"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40592,6 +40872,732 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Joep</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>BAKEL VAN</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>49779</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Martin Florian</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>SCHUBERT</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Alena</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>KOSTROMITINA</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ERLINEKOV</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>KLIMAVA</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Annesofie</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>WINTHER</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Sumit</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>SHOKEEN</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>65545</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>CONCHA</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>COELHO</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>85380</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>EPISHIN</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>FERNANDEZ CASTANON</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>97015</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Laila</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>HEINE</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>98131</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Serban Mihail</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>CICU</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>104760</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Maja</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>HORVATH</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>106866</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Alina</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>KOVALEVA</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>109339</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Joshua</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>110840</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Bertram Sollann</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SORENSEN</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>110845</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Sara Bressendorff</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>ANDERSEN</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>111198</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Isak</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>MAXSTAD</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>111770</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Nicoleta Georgiana</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>BELIBOU</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>112334</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ ALONSO</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>112336</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>GRIJALBA GUERRERO</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>112337</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>GOMEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>112350</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Carlos Gutier</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>PICON VOCES</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>112783</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>COETZER</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>116917</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Baltazar Josue</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>ITRIA</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>116921</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>CAFFA</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>116930</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Todor</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>IVANOV</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>117389</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Keiichi</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>YAMAGUCHI</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>117391</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Yukiko</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>NISHIBUN</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>118119</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Nicusor</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>STOIAN</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Ardis</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>LUDA</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Pitesti_2021_MAR/Pitesti_2021_MAR_Results.xlsx
+++ b/events/Pitesti_2021_MAR/Pitesti_2021_MAR_Results.xlsx
@@ -3114,6 +3114,11 @@
           <t>00:17:33.440</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10999,6 +11004,11 @@
           <t>00:16:16.370</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -24195,6 +24205,11 @@
       <c r="P356" t="inlineStr">
         <is>
           <t>02:06:03.050</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -33477,7 +33492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D369"/>
+  <dimension ref="A1:D370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41598,6 +41613,28 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
